--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118921592</v>
+        <v>118921474</v>
       </c>
       <c r="B2" t="n">
-        <v>90504</v>
+        <v>90531</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459221</v>
+        <v>459066</v>
       </c>
       <c r="R2" t="n">
-        <v>6703150</v>
+        <v>6703246</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118921209</v>
+        <v>118921569</v>
       </c>
       <c r="B3" t="n">
-        <v>90947</v>
+        <v>90511</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459114</v>
+        <v>459199</v>
       </c>
       <c r="R3" t="n">
-        <v>6702819</v>
+        <v>6703094</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118921619</v>
+        <v>118921394</v>
       </c>
       <c r="B4" t="n">
-        <v>90504</v>
+        <v>90954</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459351</v>
+        <v>459130</v>
       </c>
       <c r="R4" t="n">
-        <v>6703181</v>
+        <v>6703078</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118921411</v>
+        <v>118921525</v>
       </c>
       <c r="B5" t="n">
-        <v>90788</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459105</v>
+        <v>459050</v>
       </c>
       <c r="R5" t="n">
-        <v>6703128</v>
+        <v>6703248</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På äldre tallstam.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118921109</v>
+        <v>118921583</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,35 +1116,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459310</v>
+        <v>459182</v>
       </c>
       <c r="R6" t="n">
-        <v>6702890</v>
+        <v>6703086</v>
       </c>
       <c r="S6" t="n">
         <v>75</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118921641</v>
+        <v>118921185</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>90511</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,14 +1249,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väst Snarktjärn, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459363</v>
+        <v>459170</v>
       </c>
       <c r="R7" t="n">
-        <v>6703195</v>
+        <v>6702821</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1289,11 +1289,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På tallstam, riklig förekomst.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118921583</v>
+        <v>118921548</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>90795</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1364,13 +1359,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459182</v>
+        <v>459192</v>
       </c>
       <c r="R8" t="n">
-        <v>6703086</v>
+        <v>6703106</v>
       </c>
       <c r="S8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118921569</v>
+        <v>118921306</v>
       </c>
       <c r="B9" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,13 +1465,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459199</v>
+        <v>459122</v>
       </c>
       <c r="R9" t="n">
-        <v>6703094</v>
+        <v>6703132</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118921548</v>
+        <v>118921370</v>
       </c>
       <c r="B10" t="n">
-        <v>90788</v>
+        <v>90511</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,13 +1571,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459192</v>
+        <v>459112</v>
       </c>
       <c r="R10" t="n">
-        <v>6703106</v>
+        <v>6703153</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1639,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118921525</v>
+        <v>118921454</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,30 +1646,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459050</v>
+        <v>459101</v>
       </c>
       <c r="R11" t="n">
-        <v>6703248</v>
+        <v>6703170</v>
       </c>
       <c r="S11" t="n">
         <v>75</v>
@@ -1718,11 +1718,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På äldre tallstam.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118921474</v>
+        <v>118921619</v>
       </c>
       <c r="B12" t="n">
-        <v>90524</v>
+        <v>90511</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459066</v>
+        <v>459351</v>
       </c>
       <c r="R12" t="n">
-        <v>6703246</v>
+        <v>6703181</v>
       </c>
       <c r="S12" t="n">
         <v>75</v>
@@ -1856,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118921185</v>
+        <v>118921268</v>
       </c>
       <c r="B13" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459170</v>
+        <v>459122</v>
       </c>
       <c r="R13" t="n">
-        <v>6702821</v>
+        <v>6703094</v>
       </c>
       <c r="S13" t="n">
         <v>75</v>
@@ -1962,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118921231</v>
+        <v>118921209</v>
       </c>
       <c r="B14" t="n">
-        <v>90504</v>
+        <v>90954</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,25 +1969,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2005,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459071</v>
+        <v>459114</v>
       </c>
       <c r="R14" t="n">
-        <v>6703045</v>
+        <v>6702819</v>
       </c>
       <c r="S14" t="n">
         <v>75</v>
@@ -2068,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118921454</v>
+        <v>118921231</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>90511</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,35 +2075,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2116,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459101</v>
+        <v>459071</v>
       </c>
       <c r="R15" t="n">
-        <v>6703170</v>
+        <v>6703045</v>
       </c>
       <c r="S15" t="n">
         <v>75</v>
@@ -2179,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118921306</v>
+        <v>118921592</v>
       </c>
       <c r="B16" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2222,10 +2212,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459122</v>
+        <v>459221</v>
       </c>
       <c r="R16" t="n">
-        <v>6703132</v>
+        <v>6703150</v>
       </c>
       <c r="S16" t="n">
         <v>75</v>
@@ -2285,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118921370</v>
+        <v>118921109</v>
       </c>
       <c r="B17" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2297,30 +2287,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2328,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459112</v>
+        <v>459310</v>
       </c>
       <c r="R17" t="n">
-        <v>6703153</v>
+        <v>6702890</v>
       </c>
       <c r="S17" t="n">
         <v>75</v>
@@ -2391,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118921609</v>
+        <v>118921411</v>
       </c>
       <c r="B18" t="n">
-        <v>90788</v>
+        <v>90795</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2434,10 +2429,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459349</v>
+        <v>459105</v>
       </c>
       <c r="R18" t="n">
-        <v>6703191</v>
+        <v>6703128</v>
       </c>
       <c r="S18" t="n">
         <v>75</v>
@@ -2497,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118921688</v>
+        <v>118921609</v>
       </c>
       <c r="B19" t="n">
-        <v>90524</v>
+        <v>90795</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,21 +2508,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2540,10 +2535,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459490</v>
+        <v>459349</v>
       </c>
       <c r="R19" t="n">
-        <v>6702946</v>
+        <v>6703191</v>
       </c>
       <c r="S19" t="n">
         <v>75</v>
@@ -2603,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118921394</v>
+        <v>118921688</v>
       </c>
       <c r="B20" t="n">
-        <v>90947</v>
+        <v>90531</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2610,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459130</v>
+        <v>459490</v>
       </c>
       <c r="R20" t="n">
-        <v>6703078</v>
+        <v>6702946</v>
       </c>
       <c r="S20" t="n">
         <v>75</v>
@@ -2709,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118921268</v>
+        <v>118921641</v>
       </c>
       <c r="B21" t="n">
-        <v>90504</v>
+        <v>78491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2725,21 +2720,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,14 +2743,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Väst Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459122</v>
+        <v>459363</v>
       </c>
       <c r="R21" t="n">
-        <v>6703094</v>
+        <v>6703195</v>
       </c>
       <c r="S21" t="n">
         <v>75</v>
@@ -2788,6 +2783,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På tallstam, riklig förekomst.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118921474</v>
+        <v>118921548</v>
       </c>
       <c r="B2" t="n">
-        <v>90531</v>
+        <v>90795</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459066</v>
+        <v>459192</v>
       </c>
       <c r="R2" t="n">
-        <v>6703246</v>
+        <v>6703106</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118921569</v>
+        <v>118921619</v>
       </c>
       <c r="B3" t="n">
         <v>90511</v>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459199</v>
+        <v>459351</v>
       </c>
       <c r="R3" t="n">
-        <v>6703094</v>
+        <v>6703181</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118921394</v>
+        <v>118921525</v>
       </c>
       <c r="B4" t="n">
-        <v>90954</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459130</v>
+        <v>459050</v>
       </c>
       <c r="R4" t="n">
-        <v>6703078</v>
+        <v>6703248</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -966,6 +966,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På äldre tallstam.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118921525</v>
+        <v>118921641</v>
       </c>
       <c r="B5" t="n">
         <v>78491</v>
@@ -1032,14 +1037,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Väst Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459050</v>
+        <v>459363</v>
       </c>
       <c r="R5" t="n">
-        <v>6703248</v>
+        <v>6703195</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På äldre tallstam.</t>
+          <t>På tallstam, riklig förekomst.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118921583</v>
+        <v>118921370</v>
       </c>
       <c r="B6" t="n">
-        <v>78491</v>
+        <v>90511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459182</v>
+        <v>459112</v>
       </c>
       <c r="R6" t="n">
-        <v>6703086</v>
+        <v>6703153</v>
       </c>
       <c r="S6" t="n">
         <v>75</v>
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118921185</v>
+        <v>118921411</v>
       </c>
       <c r="B7" t="n">
-        <v>90511</v>
+        <v>90795</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459170</v>
+        <v>459105</v>
       </c>
       <c r="R7" t="n">
-        <v>6702821</v>
+        <v>6703128</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118921548</v>
+        <v>118921209</v>
       </c>
       <c r="B8" t="n">
-        <v>90795</v>
+        <v>90954</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,13 +1364,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459192</v>
+        <v>459114</v>
       </c>
       <c r="R8" t="n">
-        <v>6703106</v>
+        <v>6702819</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118921306</v>
+        <v>118921688</v>
       </c>
       <c r="B9" t="n">
-        <v>90511</v>
+        <v>90531</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459122</v>
+        <v>459490</v>
       </c>
       <c r="R9" t="n">
-        <v>6703132</v>
+        <v>6702946</v>
       </c>
       <c r="S9" t="n">
         <v>75</v>
@@ -1528,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118921370</v>
+        <v>118921569</v>
       </c>
       <c r="B10" t="n">
         <v>90511</v>
@@ -1571,13 +1576,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459112</v>
+        <v>459199</v>
       </c>
       <c r="R10" t="n">
-        <v>6703153</v>
+        <v>6703094</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1634,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118921454</v>
+        <v>118921306</v>
       </c>
       <c r="B11" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,35 +1651,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459101</v>
+        <v>459122</v>
       </c>
       <c r="R11" t="n">
-        <v>6703170</v>
+        <v>6703132</v>
       </c>
       <c r="S11" t="n">
         <v>75</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118921619</v>
+        <v>118921268</v>
       </c>
       <c r="B12" t="n">
         <v>90511</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459351</v>
+        <v>459122</v>
       </c>
       <c r="R12" t="n">
-        <v>6703181</v>
+        <v>6703094</v>
       </c>
       <c r="S12" t="n">
         <v>75</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118921268</v>
+        <v>118921454</v>
       </c>
       <c r="B13" t="n">
-        <v>90511</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,30 +1863,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1894,10 +1899,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459122</v>
+        <v>459101</v>
       </c>
       <c r="R13" t="n">
-        <v>6703094</v>
+        <v>6703170</v>
       </c>
       <c r="S13" t="n">
         <v>75</v>
@@ -1957,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118921209</v>
+        <v>118921185</v>
       </c>
       <c r="B14" t="n">
-        <v>90954</v>
+        <v>90511</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,25 +1974,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2000,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459114</v>
+        <v>459170</v>
       </c>
       <c r="R14" t="n">
-        <v>6702819</v>
+        <v>6702821</v>
       </c>
       <c r="S14" t="n">
         <v>75</v>
@@ -2169,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118921592</v>
+        <v>118921583</v>
       </c>
       <c r="B16" t="n">
-        <v>90511</v>
+        <v>78491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2190,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2212,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459221</v>
+        <v>459182</v>
       </c>
       <c r="R16" t="n">
-        <v>6703150</v>
+        <v>6703086</v>
       </c>
       <c r="S16" t="n">
         <v>75</v>
@@ -2275,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118921109</v>
+        <v>118921474</v>
       </c>
       <c r="B17" t="n">
-        <v>97853</v>
+        <v>90531</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,35 +2292,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459310</v>
+        <v>459066</v>
       </c>
       <c r="R17" t="n">
-        <v>6702890</v>
+        <v>6703246</v>
       </c>
       <c r="S17" t="n">
         <v>75</v>
@@ -2386,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118921411</v>
+        <v>118921109</v>
       </c>
       <c r="B18" t="n">
-        <v>90795</v>
+        <v>97853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,30 +2398,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2429,10 +2434,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459105</v>
+        <v>459310</v>
       </c>
       <c r="R18" t="n">
-        <v>6703128</v>
+        <v>6702890</v>
       </c>
       <c r="S18" t="n">
         <v>75</v>
@@ -2492,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118921609</v>
+        <v>118921592</v>
       </c>
       <c r="B19" t="n">
-        <v>90795</v>
+        <v>90511</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,21 +2513,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2535,10 +2540,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459349</v>
+        <v>459221</v>
       </c>
       <c r="R19" t="n">
-        <v>6703191</v>
+        <v>6703150</v>
       </c>
       <c r="S19" t="n">
         <v>75</v>
@@ -2598,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118921688</v>
+        <v>118921394</v>
       </c>
       <c r="B20" t="n">
-        <v>90531</v>
+        <v>90954</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2641,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459490</v>
+        <v>459130</v>
       </c>
       <c r="R20" t="n">
-        <v>6702946</v>
+        <v>6703078</v>
       </c>
       <c r="S20" t="n">
         <v>75</v>
@@ -2704,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118921641</v>
+        <v>118921609</v>
       </c>
       <c r="B21" t="n">
-        <v>78491</v>
+        <v>90795</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2720,21 +2725,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,14 +2748,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Väst Snarktjärn, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459363</v>
+        <v>459349</v>
       </c>
       <c r="R21" t="n">
-        <v>6703195</v>
+        <v>6703191</v>
       </c>
       <c r="S21" t="n">
         <v>75</v>
@@ -2783,11 +2788,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-03</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På tallstam, riklig förekomst.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -6208,10 +6208,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119674323</v>
+        <v>119674417</v>
       </c>
       <c r="B51" t="n">
-        <v>91834</v>
+        <v>91863</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6224,21 +6224,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459057</v>
+        <v>459258</v>
       </c>
       <c r="R51" t="n">
-        <v>6703073</v>
+        <v>6702997</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6314,10 +6314,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119674417</v>
+        <v>119674323</v>
       </c>
       <c r="B52" t="n">
-        <v>91863</v>
+        <v>91834</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6330,21 +6330,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459258</v>
+        <v>459057</v>
       </c>
       <c r="R52" t="n">
-        <v>6702997</v>
+        <v>6703073</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>

--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -5560,10 +5560,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119674014</v>
+        <v>119674043</v>
       </c>
       <c r="B45" t="n">
-        <v>91005</v>
+        <v>90846</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5572,28 +5572,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5603,10 +5607,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459258</v>
+        <v>459144</v>
       </c>
       <c r="R45" t="n">
-        <v>6702845</v>
+        <v>6702824</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5666,7 +5670,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119674640</v>
+        <v>119674071</v>
       </c>
       <c r="B46" t="n">
         <v>91840</v>
@@ -5699,7 +5703,11 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5709,10 +5717,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459359</v>
+        <v>459087</v>
       </c>
       <c r="R46" t="n">
-        <v>6702943</v>
+        <v>6702938</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5772,10 +5780,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119674477</v>
+        <v>119673917</v>
       </c>
       <c r="B47" t="n">
-        <v>57463</v>
+        <v>78560</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5788,27 +5796,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5816,13 +5823,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459278</v>
+        <v>459291</v>
       </c>
       <c r="R47" t="n">
-        <v>6702971</v>
+        <v>6702787</v>
       </c>
       <c r="S47" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5860,6 +5867,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5878,10 +5886,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119674393</v>
+        <v>119674323</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5890,32 +5898,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -5925,10 +5929,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459168</v>
+        <v>459057</v>
       </c>
       <c r="R48" t="n">
-        <v>6702950</v>
+        <v>6703073</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -6098,10 +6102,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119674383</v>
+        <v>119674292</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6110,32 +6114,28 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459126</v>
+        <v>459100</v>
       </c>
       <c r="R50" t="n">
-        <v>6703104</v>
+        <v>6702976</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6208,10 +6208,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119674417</v>
+        <v>119674640</v>
       </c>
       <c r="B51" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6220,25 +6220,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459258</v>
+        <v>459359</v>
       </c>
       <c r="R51" t="n">
-        <v>6702997</v>
+        <v>6702943</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6314,10 +6314,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119674323</v>
+        <v>119674417</v>
       </c>
       <c r="B52" t="n">
-        <v>91834</v>
+        <v>91863</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6330,21 +6330,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459057</v>
+        <v>459258</v>
       </c>
       <c r="R52" t="n">
-        <v>6703073</v>
+        <v>6702997</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6420,10 +6420,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119674061</v>
+        <v>119674393</v>
       </c>
       <c r="B53" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6432,28 +6432,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6463,10 +6467,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459104</v>
+        <v>459168</v>
       </c>
       <c r="R53" t="n">
-        <v>6702918</v>
+        <v>6702950</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6526,10 +6530,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119674292</v>
+        <v>119674037</v>
       </c>
       <c r="B54" t="n">
-        <v>87406</v>
+        <v>91005</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6538,28 +6542,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4412</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6569,10 +6577,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459100</v>
+        <v>459143</v>
       </c>
       <c r="R54" t="n">
-        <v>6702976</v>
+        <v>6702815</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6632,10 +6640,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119674354</v>
+        <v>119674154</v>
       </c>
       <c r="B55" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6648,26 +6656,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -6679,10 +6687,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459034</v>
+        <v>459111</v>
       </c>
       <c r="R55" t="n">
-        <v>6703098</v>
+        <v>6702980</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6742,10 +6750,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119673917</v>
+        <v>119674061</v>
       </c>
       <c r="B56" t="n">
-        <v>78560</v>
+        <v>90562</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6758,21 +6766,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6785,13 +6793,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459291</v>
+        <v>459104</v>
       </c>
       <c r="R56" t="n">
-        <v>6702787</v>
+        <v>6702918</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6848,7 +6856,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119674037</v>
+        <v>119674014</v>
       </c>
       <c r="B57" t="n">
         <v>91005</v>
@@ -6881,11 +6889,7 @@
           <t>P.Karst.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6895,13 +6899,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459143</v>
+        <v>459258</v>
       </c>
       <c r="R57" t="n">
-        <v>6702815</v>
+        <v>6702845</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6958,10 +6962,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119674071</v>
+        <v>119674354</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6970,30 +6974,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -7005,10 +7009,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459087</v>
+        <v>459034</v>
       </c>
       <c r="R58" t="n">
-        <v>6702938</v>
+        <v>6703098</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -7068,10 +7072,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119674571</v>
+        <v>119674477</v>
       </c>
       <c r="B59" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7084,30 +7088,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7115,10 +7116,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459365</v>
+        <v>459278</v>
       </c>
       <c r="R59" t="n">
-        <v>6702935</v>
+        <v>6702971</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -7159,7 +7160,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7178,10 +7178,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119674043</v>
+        <v>119674383</v>
       </c>
       <c r="B60" t="n">
-        <v>90846</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7190,30 +7190,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -7225,13 +7225,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459144</v>
+        <v>459126</v>
       </c>
       <c r="R60" t="n">
-        <v>6702824</v>
+        <v>6703104</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119674154</v>
+        <v>119674571</v>
       </c>
       <c r="B62" t="n">
         <v>91884</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459111</v>
+        <v>459365</v>
       </c>
       <c r="R62" t="n">
-        <v>6702980</v>
+        <v>6702935</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>

--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -6962,10 +6962,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119674354</v>
+        <v>119674477</v>
       </c>
       <c r="B58" t="n">
-        <v>91832</v>
+        <v>57463</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6978,30 +6978,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7009,10 +7006,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459034</v>
+        <v>459278</v>
       </c>
       <c r="R58" t="n">
-        <v>6703098</v>
+        <v>6702971</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -7053,7 +7050,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7072,10 +7068,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119674477</v>
+        <v>119674354</v>
       </c>
       <c r="B59" t="n">
-        <v>57463</v>
+        <v>91832</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7088,27 +7084,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7116,10 +7115,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459278</v>
+        <v>459034</v>
       </c>
       <c r="R59" t="n">
-        <v>6702971</v>
+        <v>6703098</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -7160,6 +7159,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -5560,10 +5560,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119674043</v>
+        <v>119673964</v>
       </c>
       <c r="B45" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5576,28 +5576,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5607,10 +5603,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459144</v>
+        <v>459282</v>
       </c>
       <c r="R45" t="n">
-        <v>6702824</v>
+        <v>6702780</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5670,10 +5666,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119674071</v>
+        <v>119674043</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>90846</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5682,30 +5678,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5717,13 +5713,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459087</v>
+        <v>459144</v>
       </c>
       <c r="R46" t="n">
-        <v>6702938</v>
+        <v>6702824</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5780,10 +5776,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119673917</v>
+        <v>119674323</v>
       </c>
       <c r="B47" t="n">
-        <v>78560</v>
+        <v>91834</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5796,21 +5792,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5823,13 +5819,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459291</v>
+        <v>459057</v>
       </c>
       <c r="R47" t="n">
-        <v>6702787</v>
+        <v>6703073</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5886,10 +5882,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119674323</v>
+        <v>119674071</v>
       </c>
       <c r="B48" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5898,28 +5894,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459057</v>
+        <v>459087</v>
       </c>
       <c r="R48" t="n">
-        <v>6703073</v>
+        <v>6702938</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -6102,10 +6102,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119674292</v>
+        <v>119674383</v>
       </c>
       <c r="B50" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6114,28 +6114,32 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -6145,10 +6149,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459100</v>
+        <v>459126</v>
       </c>
       <c r="R50" t="n">
-        <v>6702976</v>
+        <v>6703104</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6530,10 +6534,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119674037</v>
+        <v>119674061</v>
       </c>
       <c r="B54" t="n">
-        <v>91005</v>
+        <v>90562</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6542,32 +6546,28 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459143</v>
+        <v>459104</v>
       </c>
       <c r="R54" t="n">
-        <v>6702815</v>
+        <v>6702918</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6750,10 +6750,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119674061</v>
+        <v>119674477</v>
       </c>
       <c r="B56" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6766,26 +6766,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6793,10 +6794,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459104</v>
+        <v>459278</v>
       </c>
       <c r="R56" t="n">
-        <v>6702918</v>
+        <v>6702971</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6837,7 +6838,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6962,10 +6962,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119674477</v>
+        <v>119674037</v>
       </c>
       <c r="B58" t="n">
-        <v>57463</v>
+        <v>91005</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6974,31 +6974,34 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7006,10 +7009,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459278</v>
+        <v>459143</v>
       </c>
       <c r="R58" t="n">
-        <v>6702971</v>
+        <v>6702815</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -7050,6 +7053,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7068,10 +7072,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119674354</v>
+        <v>119674571</v>
       </c>
       <c r="B59" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7084,26 +7088,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -7115,10 +7119,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459034</v>
+        <v>459365</v>
       </c>
       <c r="R59" t="n">
-        <v>6703098</v>
+        <v>6702935</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -7178,10 +7182,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119674383</v>
+        <v>119674292</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7190,32 +7194,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459126</v>
+        <v>459100</v>
       </c>
       <c r="R60" t="n">
-        <v>6703104</v>
+        <v>6702976</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7288,10 +7288,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119673964</v>
+        <v>119674354</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7304,24 +7304,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7331,13 +7335,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459282</v>
+        <v>459034</v>
       </c>
       <c r="R61" t="n">
-        <v>6702780</v>
+        <v>6703098</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7394,10 +7398,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119674571</v>
+        <v>119673917</v>
       </c>
       <c r="B62" t="n">
-        <v>91884</v>
+        <v>78560</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7410,28 +7414,24 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7441,13 +7441,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459365</v>
+        <v>459291</v>
       </c>
       <c r="R62" t="n">
-        <v>6702935</v>
+        <v>6702787</v>
       </c>
       <c r="S62" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>

--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -6318,10 +6318,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119674417</v>
+        <v>119674393</v>
       </c>
       <c r="B52" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6330,28 +6330,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6361,10 +6365,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459258</v>
+        <v>459168</v>
       </c>
       <c r="R52" t="n">
-        <v>6702997</v>
+        <v>6702950</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6424,10 +6428,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119674393</v>
+        <v>119674417</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6436,32 +6440,28 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6471,10 +6471,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459168</v>
+        <v>459258</v>
       </c>
       <c r="R53" t="n">
-        <v>6702950</v>
+        <v>6702997</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6962,10 +6962,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119674037</v>
+        <v>119674571</v>
       </c>
       <c r="B58" t="n">
-        <v>91005</v>
+        <v>91884</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6974,30 +6974,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>5449</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459143</v>
+        <v>459365</v>
       </c>
       <c r="R58" t="n">
-        <v>6702815</v>
+        <v>6702935</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -7072,10 +7072,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119674571</v>
+        <v>119674037</v>
       </c>
       <c r="B59" t="n">
-        <v>91884</v>
+        <v>91005</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7084,30 +7084,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>1209</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459365</v>
+        <v>459143</v>
       </c>
       <c r="R59" t="n">
-        <v>6702935</v>
+        <v>6702815</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>

--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -5560,10 +5560,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119673964</v>
+        <v>119674354</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5576,24 +5576,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5603,13 +5607,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459282</v>
+        <v>459034</v>
       </c>
       <c r="R45" t="n">
-        <v>6702780</v>
+        <v>6703098</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5666,10 +5670,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119674043</v>
+        <v>119674477</v>
       </c>
       <c r="B46" t="n">
-        <v>90846</v>
+        <v>57463</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5682,30 +5686,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5713,13 +5714,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459144</v>
+        <v>459278</v>
       </c>
       <c r="R46" t="n">
-        <v>6702824</v>
+        <v>6702971</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5757,7 +5758,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5776,10 +5776,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119674323</v>
+        <v>119674154</v>
       </c>
       <c r="B47" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5792,24 +5792,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -5819,10 +5823,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459057</v>
+        <v>459111</v>
       </c>
       <c r="R47" t="n">
-        <v>6703073</v>
+        <v>6702980</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5882,10 +5886,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119674071</v>
+        <v>119673917</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5894,32 +5898,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -5929,13 +5929,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459087</v>
+        <v>459291</v>
       </c>
       <c r="R48" t="n">
-        <v>6702938</v>
+        <v>6702787</v>
       </c>
       <c r="S48" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5992,10 +5992,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119674335</v>
+        <v>119674417</v>
       </c>
       <c r="B49" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6008,28 +6008,24 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
@@ -6039,10 +6035,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459048</v>
+        <v>459258</v>
       </c>
       <c r="R49" t="n">
-        <v>6703082</v>
+        <v>6702997</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -6102,10 +6098,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119674383</v>
+        <v>119674323</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6114,32 +6110,28 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -6149,10 +6141,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459126</v>
+        <v>459057</v>
       </c>
       <c r="R50" t="n">
-        <v>6703104</v>
+        <v>6703073</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6212,10 +6204,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119674640</v>
+        <v>119673964</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6224,25 +6216,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6255,13 +6247,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459359</v>
+        <v>459282</v>
       </c>
       <c r="R51" t="n">
-        <v>6702943</v>
+        <v>6702780</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6318,10 +6310,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119674393</v>
+        <v>119674037</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>91005</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6330,30 +6322,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -6365,10 +6357,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459168</v>
+        <v>459143</v>
       </c>
       <c r="R52" t="n">
-        <v>6702950</v>
+        <v>6702815</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6428,10 +6420,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119674417</v>
+        <v>119674383</v>
       </c>
       <c r="B53" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6440,28 +6432,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6471,10 +6467,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459258</v>
+        <v>459126</v>
       </c>
       <c r="R53" t="n">
-        <v>6702997</v>
+        <v>6703104</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6534,10 +6530,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119674061</v>
+        <v>119674292</v>
       </c>
       <c r="B54" t="n">
-        <v>90562</v>
+        <v>87406</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6550,21 +6546,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>4412</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6577,10 +6573,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459104</v>
+        <v>459100</v>
       </c>
       <c r="R54" t="n">
-        <v>6702918</v>
+        <v>6702976</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6640,7 +6636,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119674154</v>
+        <v>119674571</v>
       </c>
       <c r="B55" t="n">
         <v>91884</v>
@@ -6675,7 +6671,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -6687,10 +6683,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459111</v>
+        <v>459365</v>
       </c>
       <c r="R55" t="n">
-        <v>6702980</v>
+        <v>6702935</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6750,10 +6746,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119674477</v>
+        <v>119674071</v>
       </c>
       <c r="B56" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6762,31 +6758,34 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6794,10 +6793,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459278</v>
+        <v>459087</v>
       </c>
       <c r="R56" t="n">
-        <v>6702971</v>
+        <v>6702938</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6838,6 +6837,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6856,10 +6856,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119674014</v>
+        <v>119674393</v>
       </c>
       <c r="B57" t="n">
-        <v>91005</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6868,28 +6868,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6899,13 +6903,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459258</v>
+        <v>459168</v>
       </c>
       <c r="R57" t="n">
-        <v>6702845</v>
+        <v>6702950</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6962,10 +6966,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119674571</v>
+        <v>119674640</v>
       </c>
       <c r="B58" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6974,32 +6978,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459365</v>
+        <v>459359</v>
       </c>
       <c r="R58" t="n">
-        <v>6702935</v>
+        <v>6702943</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -7072,10 +7072,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119674037</v>
+        <v>119674335</v>
       </c>
       <c r="B59" t="n">
-        <v>91005</v>
+        <v>91832</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7084,30 +7084,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1209</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459143</v>
+        <v>459048</v>
       </c>
       <c r="R59" t="n">
-        <v>6702815</v>
+        <v>6703082</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -7182,10 +7182,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119674292</v>
+        <v>119674014</v>
       </c>
       <c r="B60" t="n">
-        <v>87406</v>
+        <v>91005</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7194,25 +7194,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4412</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7225,13 +7225,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459100</v>
+        <v>459258</v>
       </c>
       <c r="R60" t="n">
-        <v>6702976</v>
+        <v>6702845</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7288,10 +7288,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119674354</v>
+        <v>119674061</v>
       </c>
       <c r="B61" t="n">
-        <v>91832</v>
+        <v>90562</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7304,28 +7304,24 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7335,10 +7331,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459034</v>
+        <v>459104</v>
       </c>
       <c r="R61" t="n">
-        <v>6703098</v>
+        <v>6702918</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7398,10 +7394,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119673917</v>
+        <v>119674043</v>
       </c>
       <c r="B62" t="n">
-        <v>78560</v>
+        <v>90846</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7414,24 +7410,28 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459291</v>
+        <v>459144</v>
       </c>
       <c r="R62" t="n">
-        <v>6702787</v>
+        <v>6702824</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>

--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -6966,10 +6966,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119674640</v>
+        <v>119674335</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6978,28 +6978,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -7009,10 +7013,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459359</v>
+        <v>459048</v>
       </c>
       <c r="R58" t="n">
-        <v>6702943</v>
+        <v>6703082</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -7072,10 +7076,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119674335</v>
+        <v>119674640</v>
       </c>
       <c r="B59" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7084,32 +7088,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459048</v>
+        <v>459359</v>
       </c>
       <c r="R59" t="n">
-        <v>6703082</v>
+        <v>6702943</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>

--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -6966,10 +6966,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119674335</v>
+        <v>119674640</v>
       </c>
       <c r="B58" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6978,32 +6978,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -7013,10 +7009,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459048</v>
+        <v>459359</v>
       </c>
       <c r="R58" t="n">
-        <v>6703082</v>
+        <v>6702943</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -7076,10 +7072,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119674640</v>
+        <v>119674335</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7088,28 +7084,32 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459359</v>
+        <v>459048</v>
       </c>
       <c r="R59" t="n">
-        <v>6702943</v>
+        <v>6703082</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>

--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -2944,7 +2944,7 @@
         <v>119050385</v>
       </c>
       <c r="B23" t="n">
-        <v>57308</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -2944,7 +2944,7 @@
         <v>119050385</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>118921411</v>
       </c>
       <c r="B2" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118921209</v>
+        <v>118921548</v>
       </c>
       <c r="B3" t="n">
-        <v>90956</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,13 +814,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459114</v>
+        <v>459192</v>
       </c>
       <c r="R3" t="n">
-        <v>6702819</v>
+        <v>6703106</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118921569</v>
+        <v>119050285</v>
       </c>
       <c r="B4" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +888,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Flatnan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459199</v>
+        <v>459138</v>
       </c>
       <c r="R4" t="n">
-        <v>6703094</v>
+        <v>6703072</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -960,12 +951,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,34 +975,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118921688</v>
+        <v>119674043</v>
       </c>
       <c r="B5" t="n">
-        <v>90533</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,24 +1004,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1036,13 +1035,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459490</v>
+        <v>459144</v>
       </c>
       <c r="R5" t="n">
-        <v>6702946</v>
+        <v>6702824</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,12 +1065,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,47 +1098,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118921109</v>
+        <v>118921185</v>
       </c>
       <c r="B6" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1147,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459310</v>
+        <v>459170</v>
       </c>
       <c r="R6" t="n">
-        <v>6702890</v>
+        <v>6702821</v>
       </c>
       <c r="S6" t="n">
         <v>75</v>
@@ -1210,47 +1199,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118921454</v>
+        <v>118921231</v>
       </c>
       <c r="B7" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459101</v>
+        <v>459071</v>
       </c>
       <c r="R7" t="n">
-        <v>6703170</v>
+        <v>6703045</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1321,15 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118921609</v>
+        <v>118921268</v>
       </c>
       <c r="B8" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,21 +1311,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1364,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459349</v>
+        <v>459122</v>
       </c>
       <c r="R8" t="n">
-        <v>6703191</v>
+        <v>6703094</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1427,15 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118921641</v>
+        <v>118921306</v>
       </c>
       <c r="B9" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,21 +1412,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1466,14 +1435,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väst Snarktjärn, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459363</v>
+        <v>459122</v>
       </c>
       <c r="R9" t="n">
-        <v>6703195</v>
+        <v>6703132</v>
       </c>
       <c r="S9" t="n">
         <v>75</v>
@@ -1506,11 +1475,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På tallstam, riklig förekomst.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,15 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118921583</v>
+        <v>118921370</v>
       </c>
       <c r="B10" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,21 +1513,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459182</v>
+        <v>459112</v>
       </c>
       <c r="R10" t="n">
-        <v>6703086</v>
+        <v>6703153</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>
@@ -1644,15 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118921370</v>
+        <v>119049959</v>
       </c>
       <c r="B11" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,22 +1632,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Snarktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459112</v>
+        <v>459156</v>
       </c>
       <c r="R11" t="n">
-        <v>6703153</v>
+        <v>6702984</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1717,12 +1668,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ullticka längst hela granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1731,34 +1697,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118921474</v>
+        <v>119050157</v>
       </c>
       <c r="B12" t="n">
-        <v>90533</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,40 +1726,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Flatnan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459066</v>
+        <v>459142</v>
       </c>
       <c r="R12" t="n">
-        <v>6703246</v>
+        <v>6703060</v>
       </c>
       <c r="S12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1823,12 +1780,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Längst med hela granlågan</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,34 +1809,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118921525</v>
+        <v>119050348</v>
       </c>
       <c r="B13" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,40 +1838,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Flatnan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459050</v>
+        <v>459122</v>
       </c>
       <c r="R13" t="n">
-        <v>6703248</v>
+        <v>6703147</v>
       </c>
       <c r="S13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1929,17 +1892,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På äldre tallstam.</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1948,34 +1916,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118921185</v>
+        <v>119050457</v>
       </c>
       <c r="B14" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,22 +1963,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Flatnan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459170</v>
+        <v>459068</v>
       </c>
       <c r="R14" t="n">
-        <v>6702821</v>
+        <v>6703185</v>
       </c>
       <c r="S14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2040,12 +1999,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,34 +2023,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118921548</v>
+        <v>119674061</v>
       </c>
       <c r="B15" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2089,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459192</v>
+        <v>459104</v>
       </c>
       <c r="R15" t="n">
-        <v>6703106</v>
+        <v>6702918</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2146,12 +2109,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,15 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118921268</v>
+        <v>118921209</v>
       </c>
       <c r="B16" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,21 +2153,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2222,10 +2180,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459122</v>
+        <v>459114</v>
       </c>
       <c r="R16" t="n">
-        <v>6703094</v>
+        <v>6702819</v>
       </c>
       <c r="S16" t="n">
         <v>75</v>
@@ -2264,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
@@ -2288,16 +2246,11 @@
         <v>118921394</v>
       </c>
       <c r="B17" t="n">
-        <v>90956</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2310,12 +2263,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2391,15 +2344,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118921592</v>
+        <v>119048903</v>
       </c>
       <c r="B18" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,40 +2355,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Snarktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459221</v>
+        <v>459121</v>
       </c>
       <c r="R18" t="n">
-        <v>6703150</v>
+        <v>6702763</v>
       </c>
       <c r="S18" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2464,12 +2418,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rynkskinn under granlåga, finns längst hela stammen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2478,34 +2447,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118921231</v>
+        <v>119049910</v>
       </c>
       <c r="B19" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2513,40 +2476,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Snarktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459071</v>
+        <v>459156</v>
       </c>
       <c r="R19" t="n">
-        <v>6703045</v>
+        <v>6702984</v>
       </c>
       <c r="S19" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2570,12 +2539,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Under död granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2584,34 +2568,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118921306</v>
+        <v>119674037</v>
       </c>
       <c r="B20" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,24 +2597,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2646,13 +2628,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459122</v>
+        <v>459143</v>
       </c>
       <c r="R20" t="n">
-        <v>6703132</v>
+        <v>6702815</v>
       </c>
       <c r="S20" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2676,12 +2658,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2709,15 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118921619</v>
+        <v>119674335</v>
       </c>
       <c r="B21" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,24 +2702,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2752,13 +2733,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459351</v>
+        <v>459048</v>
       </c>
       <c r="R21" t="n">
-        <v>6703181</v>
+        <v>6703082</v>
       </c>
       <c r="S21" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2782,12 +2763,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,59 +2796,52 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119049910</v>
+        <v>119674354</v>
       </c>
       <c r="B22" t="n">
-        <v>90987</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Snarktjärnen, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459156</v>
+        <v>459034</v>
       </c>
       <c r="R22" t="n">
-        <v>6702984</v>
+        <v>6703098</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2894,27 +2868,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Under död granlåga</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2923,33 +2882,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119050385</v>
+        <v>119674323</v>
       </c>
       <c r="B23" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2957,39 +2912,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Flatnan, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459120</v>
+        <v>459057</v>
       </c>
       <c r="R23" t="n">
-        <v>6703111</v>
+        <v>6703073</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3016,27 +2969,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska och gamla spår på tall ifrån tretåig hackspett</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3045,33 +2983,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119051303</v>
+        <v>119674071</v>
       </c>
       <c r="B24" t="n">
-        <v>90828</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,37 +3013,44 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Flatnan, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459349</v>
+        <v>459087</v>
       </c>
       <c r="R24" t="n">
-        <v>6703095</v>
+        <v>6702938</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3133,27 +3074,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Längst med hela granlågan</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,68 +3088,71 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119047700</v>
+        <v>119674383</v>
       </c>
       <c r="B25" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Snarktjärnen, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459307</v>
+        <v>459126</v>
       </c>
       <c r="R25" t="n">
-        <v>6702860</v>
+        <v>6703104</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3250,27 +3179,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:46</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Vedticka på smal granlåga.</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3279,33 +3193,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119048345</v>
+        <v>119674393</v>
       </c>
       <c r="B26" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3313,34 +3223,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Snarktjärnen, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459337</v>
+        <v>459168</v>
       </c>
       <c r="R26" t="n">
-        <v>6702867</v>
+        <v>6702950</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3367,27 +3284,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Garnlav på både tall och gran. Flera stammar</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3396,77 +3298,67 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119047600</v>
+        <v>119674292</v>
       </c>
       <c r="B27" t="n">
-        <v>91822</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Snarktjärnen, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459313</v>
+        <v>459100</v>
       </c>
       <c r="R27" t="n">
-        <v>6702823</v>
+        <v>6702976</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3493,27 +3385,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:46</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2 nya fruktkroppar bredvid  två gamla</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3522,80 +3399,70 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119047866</v>
+        <v>118921474</v>
       </c>
       <c r="B28" t="n">
-        <v>95184</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Snarktjärnen, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459337</v>
+        <v>459066</v>
       </c>
       <c r="R28" t="n">
-        <v>6702867</v>
+        <v>6703246</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3619,22 +3486,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,68 +3500,64 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119049959</v>
+        <v>119050480</v>
       </c>
       <c r="B29" t="n">
-        <v>90544</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Snarktjärnen, Dlr</t>
+          <t>Flatnan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459156</v>
+        <v>459049</v>
       </c>
       <c r="R29" t="n">
-        <v>6702984</v>
+        <v>6703183</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3736,7 +3589,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3746,12 +3599,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ullticka längst hela granlåga</t>
+          <t>Under Tunn granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3778,62 +3631,51 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119051270</v>
+        <v>118921525</v>
       </c>
       <c r="B30" t="n">
-        <v>91814</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Flatnan, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459370</v>
+        <v>459050</v>
       </c>
       <c r="R30" t="n">
-        <v>6703132</v>
+        <v>6703248</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3857,22 +3699,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:13</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:13</t>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På äldre tallstam.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3881,71 +3718,70 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119050348</v>
+        <v>118921583</v>
       </c>
       <c r="B31" t="n">
-        <v>90544</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Flatnan, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459122</v>
+        <v>459182</v>
       </c>
       <c r="R31" t="n">
-        <v>6703147</v>
+        <v>6703086</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3969,22 +3805,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3993,33 +3819,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119048377</v>
+        <v>119050385</v>
       </c>
       <c r="B32" t="n">
-        <v>91814</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4027,43 +3849,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Snarktjärnen, Dlr</t>
+          <t>Flatnan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459300</v>
+        <v>459120</v>
       </c>
       <c r="R32" t="n">
-        <v>6702814</v>
+        <v>6703111</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4095,7 +3913,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4105,7 +3923,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska och gamla spår på tall ifrån tretåig hackspett</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4132,15 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119051735</v>
+        <v>119049223</v>
       </c>
       <c r="B33" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4148,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4172,13 +3990,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459485</v>
+        <v>459117</v>
       </c>
       <c r="R33" t="n">
-        <v>6702932</v>
+        <v>6702886</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4207,7 +4025,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4217,12 +4035,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Längst med gammal granlåga</t>
+          <t>Spår av mindre märgborre på stående död tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4249,53 +4067,56 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119051178</v>
+        <v>118921454</v>
       </c>
       <c r="B34" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Flatnan, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459256</v>
+        <v>459101</v>
       </c>
       <c r="R34" t="n">
-        <v>6703138</v>
+        <v>6703170</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4319,27 +4140,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På flera tallar i området</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4348,80 +4154,70 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119047775</v>
+        <v>119673917</v>
       </c>
       <c r="B35" t="n">
-        <v>97806</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Snarktjärnen, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459308</v>
+        <v>459291</v>
       </c>
       <c r="R35" t="n">
-        <v>6702890</v>
+        <v>6702787</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4445,95 +4241,84 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119049223</v>
+        <v>118921609</v>
       </c>
       <c r="B36" t="n">
-        <v>8430</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Snarktjärnen, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459117</v>
+        <v>459349</v>
       </c>
       <c r="R36" t="n">
-        <v>6702886</v>
+        <v>6703191</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4557,27 +4342,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Spår av mindre märgborre på stående död tall</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4586,33 +4356,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119047484</v>
+        <v>119051042</v>
       </c>
       <c r="B37" t="n">
-        <v>91814</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4620,26 +4386,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4649,14 +4415,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Snarktjärnen, Dlr</t>
+          <t>Flatnan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459354</v>
+        <v>459210</v>
       </c>
       <c r="R37" t="n">
-        <v>6702868</v>
+        <v>6703120</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4688,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4698,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4725,62 +4491,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119048397</v>
+        <v>119051303</v>
       </c>
       <c r="B38" t="n">
-        <v>91822</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Snarktjärnen, Dlr</t>
+          <t>Flatnan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459302</v>
+        <v>459349</v>
       </c>
       <c r="R38" t="n">
-        <v>6702795</v>
+        <v>6703095</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4809,7 +4561,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4819,7 +4571,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Längst med hela granlågan</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4846,15 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119050285</v>
+        <v>118921569</v>
       </c>
       <c r="B39" t="n">
-        <v>90828</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4862,43 +4614,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Flatnan, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459138</v>
+        <v>459199</v>
       </c>
       <c r="R39" t="n">
-        <v>6703072</v>
+        <v>6703094</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4925,22 +4671,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4949,33 +4685,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119050457</v>
+        <v>118921592</v>
       </c>
       <c r="B40" t="n">
-        <v>90544</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5001,19 +4733,22 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Flatnan, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459068</v>
+        <v>459221</v>
       </c>
       <c r="R40" t="n">
-        <v>6703185</v>
+        <v>6703150</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5037,22 +4772,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5061,33 +4786,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119050157</v>
+        <v>118921619</v>
       </c>
       <c r="B41" t="n">
-        <v>90544</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5113,19 +4834,22 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Flatnan, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459142</v>
+        <v>459351</v>
       </c>
       <c r="R41" t="n">
-        <v>6703060</v>
+        <v>6703181</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5149,27 +4873,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Längst med hela granlågan</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5178,33 +4887,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119051042</v>
+        <v>119674014</v>
       </c>
       <c r="B42" t="n">
-        <v>90828</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5212,46 +4917,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Flatnan, Dlr</t>
+          <t>Väster Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459210</v>
+        <v>459258</v>
       </c>
       <c r="R42" t="n">
-        <v>6703120</v>
+        <v>6702845</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5275,22 +4974,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:57</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:57</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5299,65 +4988,61 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119048903</v>
+        <v>119047866</v>
       </c>
       <c r="B43" t="n">
-        <v>90987</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5366,10 +5051,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459121</v>
+        <v>459337</v>
       </c>
       <c r="R43" t="n">
-        <v>6702763</v>
+        <v>6702867</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5401,7 +5086,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5411,12 +5096,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rynkskinn under granlåga, finns längst hela stammen.</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5443,50 +5123,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119050480</v>
+        <v>119047484</v>
       </c>
       <c r="B44" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Flatnan, Dlr</t>
+          <t>Snarktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459049</v>
+        <v>459354</v>
       </c>
       <c r="R44" t="n">
-        <v>6703183</v>
+        <v>6702868</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5518,7 +5202,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5528,12 +5212,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Under Tunn granlåga</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5560,15 +5239,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119674354</v>
+        <v>119048377</v>
       </c>
       <c r="B45" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5595,22 +5269,24 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Snarktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459034</v>
+        <v>459300</v>
       </c>
       <c r="R45" t="n">
-        <v>6703098</v>
+        <v>6702814</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5637,12 +5313,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5651,34 +5337,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119674477</v>
+        <v>119051270</v>
       </c>
       <c r="B46" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5686,41 +5366,46 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Flatnan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459278</v>
+        <v>459370</v>
       </c>
       <c r="R46" t="n">
-        <v>6702971</v>
+        <v>6703132</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5744,12 +5429,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5764,27 +5459,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119674154</v>
+        <v>119047600</v>
       </c>
       <c r="B47" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5792,41 +5482,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Snarktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459111</v>
+        <v>459313</v>
       </c>
       <c r="R47" t="n">
-        <v>6702980</v>
+        <v>6702823</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5853,12 +5545,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2 nya fruktkroppar bredvid  två gamla</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5867,34 +5574,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119673917</v>
+        <v>119048397</v>
       </c>
       <c r="B48" t="n">
-        <v>78560</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5902,40 +5603,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Snarktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459291</v>
+        <v>459302</v>
       </c>
       <c r="R48" t="n">
-        <v>6702787</v>
+        <v>6702795</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5959,48 +5666,52 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119674417</v>
+        <v>119674640</v>
       </c>
       <c r="B49" t="n">
-        <v>91863</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6008,21 +5719,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6035,10 +5746,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459258</v>
+        <v>459359</v>
       </c>
       <c r="R49" t="n">
-        <v>6702997</v>
+        <v>6702943</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -6098,53 +5809,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119674323</v>
+        <v>119047700</v>
       </c>
       <c r="B50" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Snarktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459057</v>
+        <v>459307</v>
       </c>
       <c r="R50" t="n">
-        <v>6703073</v>
+        <v>6702860</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6171,12 +5874,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Vedticka på smal granlåga.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6185,72 +5903,63 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119673964</v>
+        <v>119051735</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Snarktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459282</v>
+        <v>459485</v>
       </c>
       <c r="R51" t="n">
-        <v>6702780</v>
+        <v>6702932</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6277,12 +5986,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Längst med gammal granlåga</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6291,63 +6015,53 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119674037</v>
+        <v>119674417</v>
       </c>
       <c r="B52" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6357,10 +6071,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459143</v>
+        <v>459258</v>
       </c>
       <c r="R52" t="n">
-        <v>6702815</v>
+        <v>6702997</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6420,60 +6134,51 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119674383</v>
+        <v>118921641</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Väst Snarktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459126</v>
+        <v>459363</v>
       </c>
       <c r="R53" t="n">
-        <v>6703104</v>
+        <v>6703195</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6497,12 +6202,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På tallstam, riklig förekomst.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6530,53 +6240,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119674292</v>
+        <v>119048345</v>
       </c>
       <c r="B54" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Snarktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459100</v>
+        <v>459337</v>
       </c>
       <c r="R54" t="n">
-        <v>6702976</v>
+        <v>6702867</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6603,12 +6305,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Garnlav på både tall och gran. Flera stammar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6617,79 +6334,66 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119674571</v>
+        <v>119051178</v>
       </c>
       <c r="B55" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Flatnan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459365</v>
+        <v>459256</v>
       </c>
       <c r="R55" t="n">
-        <v>6702935</v>
+        <v>6703138</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6713,12 +6417,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På flera tallar i området</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6727,63 +6446,53 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119674071</v>
+        <v>119673964</v>
       </c>
       <c r="B56" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -6793,13 +6502,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459087</v>
+        <v>459282</v>
       </c>
       <c r="R56" t="n">
-        <v>6702938</v>
+        <v>6702780</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6856,46 +6565,38 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119674393</v>
+        <v>119674477</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6903,10 +6604,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459168</v>
+        <v>459278</v>
       </c>
       <c r="R57" t="n">
-        <v>6702950</v>
+        <v>6702971</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6947,7 +6648,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6966,15 +6666,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119674640</v>
+        <v>119047775</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6982,37 +6677,43 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Väster Snarktjärn, Dlr</t>
+          <t>Snarktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459359</v>
+        <v>459308</v>
       </c>
       <c r="R58" t="n">
-        <v>6702943</v>
+        <v>6702890</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -7039,12 +6740,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7053,65 +6764,60 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119674335</v>
+        <v>118921109</v>
       </c>
       <c r="B59" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7119,13 +6825,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459048</v>
+        <v>459310</v>
       </c>
       <c r="R59" t="n">
-        <v>6703082</v>
+        <v>6702890</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7149,12 +6855,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7179,328 +6885,6 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>119674014</v>
-      </c>
-      <c r="B60" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Väster Snarktjärn, Dlr</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>459258</v>
-      </c>
-      <c r="R60" t="n">
-        <v>6702845</v>
-      </c>
-      <c r="S60" t="n">
-        <v>25</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Vansbro</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Järna</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>119674061</v>
-      </c>
-      <c r="B61" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Väster Snarktjärn, Dlr</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>459104</v>
-      </c>
-      <c r="R61" t="n">
-        <v>6702918</v>
-      </c>
-      <c r="S61" t="n">
-        <v>50</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Vansbro</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Järna</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>119674043</v>
-      </c>
-      <c r="B62" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>658</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Väster Snarktjärn, Dlr</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>459144</v>
-      </c>
-      <c r="R62" t="n">
-        <v>6702824</v>
-      </c>
-      <c r="S62" t="n">
-        <v>25</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Vansbro</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Järna</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30543-2024 artfynd.xlsx
+++ b/artfynd/A 30543-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119673917</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921411</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921548</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921609</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119050285</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119051042</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119051303</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674043</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921185</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921231</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1828,6 +1883,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921268</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1929,6 +1989,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921306</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2030,6 +2095,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921370</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2131,6 +2201,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921569</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2232,6 +2307,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921592</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2333,6 +2413,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921619</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2445,6 +2530,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119049959</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2557,6 +2647,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119050157</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2664,6 +2759,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119050348</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2771,6 +2871,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119050457</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2872,6 +2977,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674061</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2973,6 +3083,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921209</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3074,6 +3189,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921394</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3195,6 +3315,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119048903</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3316,6 +3441,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119049910</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3417,6 +3547,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674014</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3522,6 +3657,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674037</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3638,6 +3778,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119047866</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3754,6 +3899,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119047484</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3870,6 +4020,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119048377</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3986,6 +4141,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119051270</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4091,6 +4251,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674335</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4196,6 +4361,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674354</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4297,6 +4467,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674323</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4418,6 +4593,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119047600</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4534,6 +4714,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119048397</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4639,6 +4824,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674071</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4744,6 +4934,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674383</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4849,6 +5044,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674393</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4950,6 +5150,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674640</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5051,6 +5256,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674292</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5152,6 +5362,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921474</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5264,6 +5479,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119047700</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5376,6 +5596,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119050480</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5488,6 +5713,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119051735</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5589,6 +5819,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674417</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5695,6 +5930,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921525</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5796,6 +6036,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921583</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5902,6 +6147,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921641</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6014,6 +6264,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119048345</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6126,6 +6381,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119051178</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6227,6 +6487,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119673964</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6344,6 +6609,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119050385</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6445,6 +6715,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119674477</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6557,6 +6832,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119049223</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6673,6 +6953,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119047775</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6779,6 +7064,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921109</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6885,8 +7175,73 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118921454</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>